--- a/MetaData/Tour de Suisse.xlsx
+++ b/MetaData/Tour de Suisse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="2012" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="253">
   <si>
     <t>NUM</t>
   </si>
@@ -779,6 +779,14 @@
   </si>
   <si>
     <t>1123.71 Km</t>
+  </si>
+  <si>
+    <t>NUM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1108,7 +1116,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1136,8 +1144,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1166,7 +1174,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
@@ -1195,7 +1203,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -1224,7 +1232,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1253,7 +1261,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -1282,7 +1290,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1311,7 +1319,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1340,7 +1348,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
@@ -1369,7 +1377,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
@@ -2471,8 +2479,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -2501,7 +2509,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -2530,7 +2538,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -2559,7 +2567,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -2588,7 +2596,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -2617,7 +2625,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -2646,7 +2654,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
@@ -2675,7 +2683,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -2704,7 +2712,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -2888,7 +2896,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2916,8 +2924,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -2946,7 +2954,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -2975,7 +2983,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -3004,7 +3012,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -3033,7 +3041,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -3062,7 +3070,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -3091,7 +3099,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -3120,7 +3128,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -3149,7 +3157,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>

--- a/MetaData/Tour de Suisse.xlsx
+++ b/MetaData/Tour de Suisse.xlsx
@@ -4,17 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2012" sheetId="1" r:id="rId1"/>
-    <sheet name="2013" sheetId="2" r:id="rId2"/>
-    <sheet name="2014" sheetId="3" r:id="rId3"/>
-    <sheet name="2015" sheetId="4" r:id="rId4"/>
-    <sheet name="2016" sheetId="5" r:id="rId5"/>
-    <sheet name="2017" sheetId="6" r:id="rId6"/>
-    <sheet name="2018" sheetId="7" r:id="rId7"/>
-    <sheet name="2019" sheetId="8" r:id="rId8"/>
+    <sheet name="2009" sheetId="9" r:id="rId1"/>
+    <sheet name="2010" sheetId="10" r:id="rId2"/>
+    <sheet name="2011" sheetId="11" r:id="rId3"/>
+    <sheet name="2012" sheetId="1" r:id="rId4"/>
+    <sheet name="2013" sheetId="2" r:id="rId5"/>
+    <sheet name="2014" sheetId="3" r:id="rId6"/>
+    <sheet name="2015" sheetId="4" r:id="rId7"/>
+    <sheet name="2016" sheetId="5" r:id="rId8"/>
+    <sheet name="2017" sheetId="6" r:id="rId9"/>
+    <sheet name="2018" sheetId="7" r:id="rId10"/>
+    <sheet name="2019" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="255">
   <si>
     <t>NUM</t>
   </si>
@@ -43,18 +46,6 @@
     <t>LENGTH</t>
   </si>
   <si>
-    <t>COMMENTS</t>
-  </si>
-  <si>
-    <t>VIEWS</t>
-  </si>
-  <si>
-    <t>STAGE ACCURACY</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -67,27 +58,15 @@
     <t>Lugano &gt; Lugano</t>
   </si>
   <si>
-    <t>7.43 Km</t>
-  </si>
-  <si>
-    <t>Final maps</t>
-  </si>
-  <si>
     <t>  </t>
   </si>
   <si>
-    <t>High mountain</t>
-  </si>
-  <si>
     <t>Sunday 10 June 2012</t>
   </si>
   <si>
     <t>Verbania (I) &gt; Verbier</t>
   </si>
   <si>
-    <t>218.72 Km</t>
-  </si>
-  <si>
     <t>Plain</t>
   </si>
   <si>
@@ -97,9 +76,6 @@
     <t>Martigny &gt; Aarberg</t>
   </si>
   <si>
-    <t>196.15 Km</t>
-  </si>
-  <si>
     <t>Medium Mountain</t>
   </si>
   <si>
@@ -109,60 +85,39 @@
     <t>Aarberg &gt; Trimbach/Olten</t>
   </si>
   <si>
-    <t>189.46 Km</t>
-  </si>
-  <si>
     <t>Wednesday 13 June 2012</t>
   </si>
   <si>
     <t>Olten/Trimbach &gt; Gansingen</t>
   </si>
   <si>
-    <t>193.45 Km</t>
-  </si>
-  <si>
     <t>Thursday 14 June 2012</t>
   </si>
   <si>
     <t>Wittnau &gt; Bischofszell (TG)</t>
   </si>
   <si>
-    <t>197.50 Km</t>
-  </si>
-  <si>
     <t>Friday 15 June 2012</t>
   </si>
   <si>
     <t>Gossau ZH &gt; Gossau ZH</t>
   </si>
   <si>
-    <t>34.35 Km</t>
-  </si>
-  <si>
     <t>Saturday 16 June 2012</t>
   </si>
   <si>
     <t>Bischofszell (TG) &gt; Arosa</t>
   </si>
   <si>
-    <t>148.21 Km</t>
-  </si>
-  <si>
     <t>Sunday 17 June 2012</t>
   </si>
   <si>
     <t>Näfels - Lintharena &gt; Sörenberg</t>
   </si>
   <si>
-    <t>215.27 Km</t>
-  </si>
-  <si>
     <t>Total distance</t>
   </si>
   <si>
-    <t>1400.54 Km</t>
-  </si>
-  <si>
     <t>Top finishes</t>
   </si>
   <si>
@@ -220,572 +175,716 @@
     <t>Quinto &gt; Quinto</t>
   </si>
   <si>
-    <t>8.14 Km</t>
-  </si>
-  <si>
-    <t>Final roadbook</t>
-  </si>
-  <si>
     <t>Sunday 9 June 2013</t>
   </si>
   <si>
-    <t>Quinto &gt; Crans-Montana</t>
-  </si>
-  <si>
-    <t>160.80 Km</t>
-  </si>
-  <si>
     <t>Monday 10 June 2013</t>
   </si>
   <si>
     <t>Montreux &gt; Meiringen</t>
   </si>
   <si>
-    <t>207.46 Km</t>
-  </si>
-  <si>
     <t>Tuesday 11 June 2013</t>
   </si>
   <si>
     <t>Innertkirchen &gt; Buochs</t>
   </si>
   <si>
-    <t>175.68 Km</t>
-  </si>
-  <si>
     <t>Wednesday 12 June 2013</t>
   </si>
   <si>
     <t>Buochs &gt; Leuggern</t>
   </si>
   <si>
-    <t>176.60 Km</t>
-  </si>
-  <si>
     <t>Thursday 13 June 2013</t>
   </si>
   <si>
     <t>Leuggern &gt; Meilen</t>
   </si>
   <si>
-    <t>188.02 Km</t>
-  </si>
-  <si>
     <t>Friday 14 June 2013</t>
   </si>
   <si>
     <t>Meilen &gt; La Punt</t>
   </si>
   <si>
-    <t>204.90 Km</t>
-  </si>
-  <si>
     <t>Saturday 15 June 2013</t>
   </si>
   <si>
     <t>Zernez &gt; Bad Ragaz</t>
   </si>
   <si>
-    <t>180.83 Km</t>
-  </si>
-  <si>
     <t>Sunday 16 June 2013</t>
   </si>
   <si>
     <t>Bad Ragaz &gt; Flumserberg</t>
   </si>
   <si>
-    <t>26.96 Km</t>
-  </si>
-  <si>
-    <t>1329.39 Km</t>
-  </si>
-  <si>
     <t>Saturday 14 June 2014</t>
   </si>
   <si>
     <t>Bellinzona &gt; Bellinzona</t>
   </si>
   <si>
-    <t>9.28 Km</t>
-  </si>
-  <si>
     <t>Sunday 15 June 2014</t>
   </si>
   <si>
     <t>Bellinzona &gt; Sarnen</t>
   </si>
   <si>
-    <t>180.77 Km</t>
-  </si>
-  <si>
     <t>Monday 16 June 2014</t>
   </si>
   <si>
     <t>Sarnen &gt; Heiden</t>
   </si>
   <si>
-    <t>206.14 Km</t>
-  </si>
-  <si>
     <t>Tuesday 17 June 2014</t>
   </si>
   <si>
     <t>Heiden &gt; Ossingen</t>
   </si>
   <si>
-    <t>159.05 Km</t>
-  </si>
-  <si>
     <t>Wednesday 18 June 2014</t>
   </si>
   <si>
     <t>Ossingen &gt; Büren an der Aare</t>
   </si>
   <si>
-    <t>183.60 Km</t>
-  </si>
-  <si>
     <t>Thursday 19 June 2014</t>
   </si>
   <si>
     <t>Büren an der Aare &gt; Delémont</t>
   </si>
   <si>
-    <t>193.18 Km</t>
-  </si>
-  <si>
     <t>Friday 20 June 2014</t>
   </si>
   <si>
     <t>Worb &gt; Worb</t>
   </si>
   <si>
-    <t>24.38 Km</t>
-  </si>
-  <si>
     <t>Saturday 21 June 2014</t>
   </si>
   <si>
     <t>Delémont &gt; Verbier</t>
   </si>
   <si>
-    <t>219.68 Km</t>
-  </si>
-  <si>
     <t>Sunday 22 June 2014</t>
   </si>
   <si>
     <t>Martigny &gt; Saas-Fee</t>
   </si>
   <si>
-    <t>156.53 Km</t>
-  </si>
-  <si>
-    <t>1332.61 Km</t>
-  </si>
-  <si>
     <t>Saturday 13 June 2015</t>
   </si>
   <si>
     <t>Risch-Rotkreuz &gt; Risch-Rotkreuz</t>
   </si>
   <si>
-    <t>4.99 Km</t>
-  </si>
-  <si>
-    <t>Inserted</t>
-  </si>
-  <si>
     <t>Sunday 14 June 2015</t>
   </si>
   <si>
-    <t>161.03 Km</t>
-  </si>
-  <si>
     <t>Monday 15 June 2015</t>
   </si>
   <si>
     <t>Quinto &gt; Olivone</t>
   </si>
   <si>
-    <t>117.17 Km</t>
-  </si>
-  <si>
     <t>Tuesday 16 June 2015</t>
   </si>
   <si>
     <t>Flims &gt; Schwarzenbach</t>
   </si>
   <si>
-    <t>193.71 Km</t>
-  </si>
-  <si>
     <t>Wednesday 17 June 2015</t>
   </si>
   <si>
     <t>Unterterzen &gt; Solden/Rettenbachferner</t>
   </si>
   <si>
-    <t>236.78 Km</t>
-  </si>
-  <si>
     <t>Thursday 18 June 2015</t>
   </si>
   <si>
     <t>Wil &gt; Bienne/Biel</t>
   </si>
   <si>
-    <t>193.93 Km</t>
-  </si>
-  <si>
     <t>Friday 19 June 2015</t>
   </si>
   <si>
     <t>Bienne/Biel &gt; Dudingen</t>
   </si>
   <si>
-    <t>164.69 Km</t>
-  </si>
-  <si>
     <t>Saturday 20 June 2015</t>
   </si>
   <si>
     <t>Bern &gt; Bern</t>
   </si>
   <si>
-    <t>150.84 Km</t>
-  </si>
-  <si>
     <t>Sunday 21 June 2015</t>
   </si>
   <si>
-    <t>37.28 Km</t>
-  </si>
-  <si>
-    <t>1260.42 Km</t>
-  </si>
-  <si>
     <t>Saturday 11 June 2016</t>
   </si>
   <si>
     <t>Baar &gt; Baar</t>
   </si>
   <si>
-    <t>6.50 Km</t>
-  </si>
-  <si>
     <t>Sunday 12 June 2016</t>
   </si>
   <si>
-    <t>187.60 Km</t>
-  </si>
-  <si>
     <t>Monday 13 June 2016</t>
   </si>
   <si>
     <t>Grosswangen &gt; Rheinfelden</t>
   </si>
   <si>
-    <t>192.59 Km</t>
-  </si>
-  <si>
     <t>Tuesday 14 June 2016</t>
   </si>
   <si>
     <t>Rheinfelden &gt; Champagne</t>
   </si>
   <si>
-    <t>192.82 Km</t>
-  </si>
-  <si>
     <t>Wednesday 15 June 2016</t>
   </si>
   <si>
     <t>Brig-Glis &gt; Carì</t>
   </si>
   <si>
-    <t>126.39 Km</t>
-  </si>
-  <si>
     <t>Thursday 16 June 2016</t>
   </si>
   <si>
     <t>Weesen &gt; Amden</t>
   </si>
   <si>
-    <t>162.88 Km</t>
-  </si>
-  <si>
     <t>Friday 17 June 2016</t>
   </si>
   <si>
     <t>Arbon &gt; Sölden</t>
   </si>
   <si>
-    <t>224.32 Km</t>
-  </si>
-  <si>
     <t>Saturday 18 June 2016</t>
   </si>
   <si>
     <t>Davos &gt; Davos</t>
   </si>
   <si>
-    <t>16.80 Km</t>
-  </si>
-  <si>
     <t>Sunday 19 June 2016</t>
   </si>
   <si>
-    <t>117.68 Km</t>
-  </si>
-  <si>
-    <t>1227.58 Km</t>
-  </si>
-  <si>
     <t>Saturday 10 June 2017</t>
   </si>
   <si>
     <t>Cham &gt; Cham</t>
   </si>
   <si>
-    <t>6.06 Km</t>
-  </si>
-  <si>
     <t>Sunday 11 June 2017</t>
   </si>
   <si>
-    <t>172.03 Km</t>
-  </si>
-  <si>
     <t>Monday 12 June 2017</t>
   </si>
   <si>
     <t>Menziken &gt; Bern</t>
   </si>
   <si>
-    <t>158.07 Km</t>
-  </si>
-  <si>
     <t>Tuesday 13 June 2017</t>
   </si>
   <si>
     <t>Bern &gt; Villars-sur-Ollon</t>
   </si>
   <si>
-    <t>150.16 Km</t>
-  </si>
-  <si>
     <t>Wednesday 14 June 2017</t>
   </si>
   <si>
     <t>Bex &gt; Cevio</t>
   </si>
   <si>
-    <t>219.70 Km</t>
-  </si>
-  <si>
     <t>Thursday 15 June 2017</t>
   </si>
   <si>
     <t>Locarno &gt; La Punt</t>
   </si>
   <si>
-    <t>166.11 Km</t>
-  </si>
-  <si>
     <t>Friday 16 June 2017</t>
   </si>
   <si>
     <t>Zernez &gt; Sölden</t>
   </si>
   <si>
-    <t>160.92 Km</t>
-  </si>
-  <si>
     <t>Saturday 17 June 2017</t>
   </si>
   <si>
     <t>Schaffhausen &gt; Schaffhausen</t>
   </si>
   <si>
-    <t>100.16 Km</t>
-  </si>
-  <si>
     <t>Sunday 18 June 2017</t>
   </si>
   <si>
-    <t>28.65 Km</t>
-  </si>
-  <si>
-    <t>1161.86 Km</t>
-  </si>
-  <si>
     <t>Saturday 9 June 2018</t>
   </si>
   <si>
     <t>Frauenfeld &gt; Frauenfeld</t>
   </si>
   <si>
-    <t>18.26 Km</t>
-  </si>
-  <si>
     <t>Sunday 10 June 2018</t>
   </si>
   <si>
-    <t>156.47 Km</t>
-  </si>
-  <si>
     <t>Monday 11 June 2018</t>
   </si>
   <si>
     <t>Oberstammheim &gt; Gansingen</t>
   </si>
   <si>
-    <t>182.98 Km</t>
-  </si>
-  <si>
     <t>Tuesday 12 June 2018</t>
   </si>
   <si>
     <t>Gansingen &gt; Gstaad</t>
   </si>
   <si>
-    <t>190.72 Km</t>
-  </si>
-  <si>
     <t>Wednesday 13 June 2018</t>
   </si>
   <si>
     <t>Gstaad &gt; Leukerbad</t>
   </si>
   <si>
-    <t>154.63 Km</t>
-  </si>
-  <si>
     <t>Thursday 14 June 2018</t>
   </si>
   <si>
     <t>Fiesch &gt; Gommiswald</t>
   </si>
   <si>
-    <t>186.00 Km</t>
-  </si>
-  <si>
     <t>Friday 15 June 2018</t>
   </si>
   <si>
     <t>Eschenbach/Atzmanning &gt; Arosa</t>
   </si>
   <si>
-    <t>170.52 Km</t>
-  </si>
-  <si>
     <t>Saturday 16 June 2018</t>
   </si>
   <si>
-    <t>120.14 Km</t>
-  </si>
-  <si>
     <t>Sunday 17 June 2018</t>
   </si>
   <si>
-    <t>34.32 Km</t>
-  </si>
-  <si>
-    <t>1214.04 Km</t>
-  </si>
-  <si>
     <t>Saturday 15 June 2019</t>
   </si>
   <si>
     <t>Langnau im Emmental &gt; Langnau i.E</t>
   </si>
   <si>
-    <t>9.56 Km</t>
-  </si>
-  <si>
     <t>Sunday 16 June 2019</t>
   </si>
   <si>
     <t>Langnau i.E. &gt; Langnau i.E.</t>
   </si>
   <si>
-    <t>157.53 Km</t>
-  </si>
-  <si>
     <t>Monday 17 June 2019</t>
   </si>
   <si>
     <t>Flamatt &gt; Murten</t>
   </si>
   <si>
-    <t>161.28 Km</t>
-  </si>
-  <si>
     <t>Tuesday 18 June 2019</t>
   </si>
   <si>
     <t>Murten &gt; Arlesheim</t>
   </si>
   <si>
-    <t>162.12 Km</t>
-  </si>
-  <si>
     <t>Wednesday 19 June 2019</t>
   </si>
   <si>
     <t>Münchenstein &gt; Einsiedeln</t>
   </si>
   <si>
-    <t>174.21 Km</t>
-  </si>
-  <si>
     <t>Thursday 20 June 2019</t>
   </si>
   <si>
     <t>Einsiedeln &gt; Flumserberg</t>
   </si>
   <si>
-    <t>121.86 Km</t>
-  </si>
-  <si>
     <t>Friday 21 June 2019</t>
   </si>
   <si>
     <t>Unterterzen &gt; San Gottardo</t>
   </si>
   <si>
-    <t>216.64 Km</t>
-  </si>
-  <si>
     <t>Saturday 22 June 2019</t>
   </si>
   <si>
     <t>Goms &gt; Goms</t>
   </si>
   <si>
-    <t>19.22 Km</t>
-  </si>
-  <si>
     <t>Sunday 23 June 2019</t>
   </si>
   <si>
     <t>Ulrichen &gt; Ulrichen</t>
   </si>
   <si>
-    <t>101.29 Km</t>
-  </si>
-  <si>
-    <t>1123.71 Km</t>
-  </si>
-  <si>
     <t>NUM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>NUM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturday 13 June 2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monday 15 June 2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tuesday 16 June 2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wednesday 17 June 2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thursday 18 June 2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Friday 19 June 2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturday 20 June 2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunday 21 June 2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mauren (Lie) &gt; Ruggell (Lie)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Davos &gt; Davos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Davos &gt; Lumino</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Biasca &gt; Stäfa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oberriet &gt; Bad Zurzach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bad Zurzach &gt; Vallorbe/Juraparc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Le Sentier/Vallée de Joux &gt; Crans-Montana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bern &gt; Bern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturday 12 June 2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunday 14 June 2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunday 13 June 2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monday 14 June 2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tuesday 15 June 2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wednesday 16 June 2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thursday 17 June 2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Friday 18 June 2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturday 19 June 2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunday 20 June 2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ascona &gt; Sierre</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sierre &gt; Schwarzenburg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Schwarzenburg &gt; Wettingen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wettingen &gt; Frutigen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Savognin &gt; Wetzikon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wetzikon &gt; Liestal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturday 11 June 2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunday 12 June 2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monday 13 June 2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tuesday 14 June 2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wednesday 15 June 2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thursday 16 June 2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Friday 17 June 2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturday 18 June 2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunday 19 June 2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Airolo &gt; Crans-Montana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brig-Glis &gt; Grindelwald</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grindelwald &gt; Huttwil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huttwil &gt; Tobel-Tägerschen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tobel-Tägerschen &gt; Triesenberg (Lie)/Malbun (Lie)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vaduz (Lie) &gt; Serfaus-Fiss-Ladis (Oe)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tübach &gt; Schaffhausen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stäfa &gt; Serfaus (Oe)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ulrichen &gt; Crans-Montana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shortened due to snow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Official</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>La FlammeRouge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProcyclingStats</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wikipedia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final Decision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>La Punt &gt; Davos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shortened since start moved to La Punt due to snow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>confirmed by official timetable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Team Time Trial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Official</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>La FlammeRouge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProcyclingStats</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wikipedia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Mountain</t>
+  </si>
+  <si>
+    <t>Medium Mountain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Mountain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medium Mountain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Mountain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Mountain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medium Mountain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Mountain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REMARKS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REMARKS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REMARKS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REMARKS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REMARKS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lugano &gt; Lugano</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Liestal &gt; Liestal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lugano &gt; Lugano</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Schaffhausen &gt; Schaffhausen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meiringen &gt; La Punt</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1116,7 +1215,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>251</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1131,16 +1230,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -1148,28 +1238,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>60</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
+        <v>172</v>
+      </c>
+      <c r="E2">
+        <v>7.8</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1177,28 +1258,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>235</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>57</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
+        <v>173</v>
+      </c>
+      <c r="E3">
+        <v>149.80000000000001</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1206,28 +1278,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>53</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
+        <v>174</v>
+      </c>
+      <c r="E4">
+        <v>195.4</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1235,28 +1298,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>236</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>53</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
+        <v>175</v>
+      </c>
+      <c r="E5">
+        <v>196.6</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1264,28 +1318,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>45</v>
-      </c>
-      <c r="H6" t="s">
-        <v>14</v>
+        <v>212</v>
+      </c>
+      <c r="E6">
+        <v>201.5</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1293,28 +1338,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>235</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>50</v>
-      </c>
-      <c r="H7" t="s">
-        <v>14</v>
+        <v>176</v>
+      </c>
+      <c r="E7">
+        <v>178</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1322,28 +1358,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>50</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
+        <v>177</v>
+      </c>
+      <c r="E8">
+        <v>204.1</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1351,28 +1378,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>235</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>51</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
+        <v>178</v>
+      </c>
+      <c r="E9">
+        <v>181.7</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -1380,49 +1398,40 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>67</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
+        <v>179</v>
+      </c>
+      <c r="E10">
+        <v>38.5</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>44</v>
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1353.4</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1430,23 +1439,23 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1454,23 +1463,23 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -1478,15 +1487,15 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>41.78</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1494,7 +1503,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1502,15 +1511,702 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E24">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>57</v>
+        <v>41</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1" t="s">
+        <v>231</v>
+      </c>
+      <c r="K1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4">
+        <v>182.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5">
+        <v>189.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6">
+        <v>155.69999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E7">
+        <v>186</v>
+      </c>
+      <c r="G7" t="s">
+        <v>232</v>
+      </c>
+      <c r="H7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I7" t="s">
+        <v>233</v>
+      </c>
+      <c r="J7" t="s">
+        <v>233</v>
+      </c>
+      <c r="K7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8">
+        <v>170.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9">
+        <v>123.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1215.4000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3">
+        <v>159.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4">
+        <v>162.30000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5">
+        <v>163.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7">
+        <v>112.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8">
+        <v>216.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1121.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>41</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -1518,7 +2214,7 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1526,26 +2222,26 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E28">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1561,7 +2257,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1576,16 +2272,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -1593,28 +2280,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>47</v>
-      </c>
-      <c r="H2" t="s">
-        <v>65</v>
+        <v>250</v>
+      </c>
+      <c r="E2">
+        <v>7.6</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1622,28 +2300,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>65</v>
-      </c>
-      <c r="H3" t="s">
-        <v>65</v>
+        <v>190</v>
+      </c>
+      <c r="E3">
+        <v>167.5</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1651,28 +2320,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>241</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>68</v>
-      </c>
-      <c r="H4" t="s">
-        <v>65</v>
+        <v>191</v>
+      </c>
+      <c r="E4">
+        <v>196.6</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1680,28 +2340,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>44</v>
-      </c>
-      <c r="H5" t="s">
-        <v>65</v>
+        <v>192</v>
+      </c>
+      <c r="E5">
+        <v>192.2</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1709,28 +2360,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>49</v>
-      </c>
-      <c r="H6" t="s">
-        <v>65</v>
+        <v>193</v>
+      </c>
+      <c r="E6">
+        <v>172.5</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1738,28 +2380,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>239</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>52</v>
-      </c>
-      <c r="H7" t="s">
-        <v>65</v>
+        <v>254</v>
+      </c>
+      <c r="E7">
+        <v>213.5</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1767,28 +2400,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>60</v>
-      </c>
-      <c r="H8" t="s">
-        <v>65</v>
+        <v>194</v>
+      </c>
+      <c r="E8">
+        <v>204.1</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1796,28 +2420,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>51</v>
-      </c>
-      <c r="H9" t="s">
-        <v>65</v>
+        <v>195</v>
+      </c>
+      <c r="E9">
+        <v>172.4</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -1825,57 +2440,48 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>189</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>60</v>
-      </c>
-      <c r="H10" t="s">
-        <v>65</v>
+        <v>251</v>
+      </c>
+      <c r="E10">
+        <v>26.9</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>90</v>
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1353.3</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1883,23 +2489,23 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -1907,7 +2513,7 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1915,7 +2521,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -1923,15 +2529,15 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>35.1</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1939,7 +2545,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1947,15 +2553,15 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E24">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -1963,15 +2569,15 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -1979,23 +2585,24 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2006,7 +2613,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2021,16 +2628,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -2038,28 +2636,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>52</v>
-      </c>
-      <c r="H2" t="s">
-        <v>65</v>
+        <v>252</v>
+      </c>
+      <c r="E2">
+        <v>7.3</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -2067,28 +2656,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>197</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>67</v>
-      </c>
-      <c r="H3" t="s">
-        <v>65</v>
+        <v>205</v>
+      </c>
+      <c r="E3">
+        <v>149</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -2096,28 +2676,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>55</v>
-      </c>
-      <c r="H4" t="s">
-        <v>65</v>
+        <v>206</v>
+      </c>
+      <c r="E4">
+        <v>107.6</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -2125,28 +2696,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>53</v>
-      </c>
-      <c r="H5" t="s">
-        <v>65</v>
+        <v>207</v>
+      </c>
+      <c r="E5">
+        <v>198.4</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -2154,28 +2716,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>43</v>
-      </c>
-      <c r="H6" t="s">
-        <v>65</v>
+        <v>208</v>
+      </c>
+      <c r="E6">
+        <v>204.2</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -2183,28 +2736,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>50</v>
-      </c>
-      <c r="H7" t="s">
-        <v>65</v>
+        <v>209</v>
+      </c>
+      <c r="E7">
+        <v>157.69999999999999</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -2212,28 +2756,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>239</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>202</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>49</v>
-      </c>
-      <c r="H8" t="s">
-        <v>65</v>
+        <v>210</v>
+      </c>
+      <c r="E8">
+        <v>222.8</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -2241,28 +2776,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>203</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>51</v>
-      </c>
-      <c r="H9" t="s">
-        <v>65</v>
+        <v>211</v>
+      </c>
+      <c r="E9">
+        <v>167.3</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -2270,65 +2796,56 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>73</v>
-      </c>
-      <c r="H10" t="s">
-        <v>65</v>
+        <v>253</v>
+      </c>
+      <c r="E10">
+        <v>32.1</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>118</v>
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1246.4000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -2336,7 +2853,7 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2344,15 +2861,15 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2360,7 +2877,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2368,15 +2885,15 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>33.659999999999997</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2384,7 +2901,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2392,15 +2909,15 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E24">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -2408,7 +2925,7 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -2416,26 +2933,26 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2446,12 +2963,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2466,322 +2983,205 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>133</v>
-      </c>
-      <c r="H2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>123</v>
-      </c>
       <c r="D3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>192</v>
-      </c>
-      <c r="H3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="E3">
+        <v>218.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>192</v>
-      </c>
-      <c r="H4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>194.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>145</v>
-      </c>
-      <c r="H5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>188.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E6" t="s">
-        <v>133</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>188</v>
-      </c>
-      <c r="H6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>192.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
-        <v>134</v>
-      </c>
       <c r="D7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" t="s">
-        <v>136</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>159</v>
-      </c>
-      <c r="H7" t="s">
-        <v>122</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>198.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>144</v>
-      </c>
-      <c r="H8" t="s">
-        <v>122</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>34.299999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>140</v>
-      </c>
       <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>156</v>
-      </c>
-      <c r="H9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="E9">
+        <v>148.19999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>234</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>174</v>
-      </c>
-      <c r="H10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="E10">
+        <v>215.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1398.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2789,7 +3189,7 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2797,7 +3197,7 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2805,7 +3205,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2813,15 +3213,15 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>42.27</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2829,7 +3229,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2837,31 +3237,31 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -2869,7 +3269,7 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E28">
         <v>11</v>
@@ -2877,10 +3277,10 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2896,7 +3296,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2911,16 +3311,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -2928,28 +3319,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>280</v>
-      </c>
-      <c r="H2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="E2">
+        <v>8.1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -2957,28 +3339,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>286</v>
-      </c>
-      <c r="H3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
+        <v>213</v>
+      </c>
+      <c r="E3">
+        <v>117.2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -2986,28 +3359,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>274</v>
-      </c>
-      <c r="H4" t="s">
-        <v>122</v>
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <v>204.9</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3015,28 +3379,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>292</v>
-      </c>
-      <c r="H5" t="s">
-        <v>122</v>
+        <v>52</v>
+      </c>
+      <c r="E5">
+        <v>174.4</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -3044,28 +3399,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>358</v>
-      </c>
-      <c r="H6" t="s">
-        <v>122</v>
+        <v>54</v>
+      </c>
+      <c r="E6">
+        <v>178.4</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -3073,28 +3419,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>319</v>
-      </c>
-      <c r="H7" t="s">
-        <v>122</v>
+        <v>56</v>
+      </c>
+      <c r="E7">
+        <v>187.9</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -3102,28 +3439,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c r="C8" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E8" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>331</v>
-      </c>
-      <c r="H8" t="s">
-        <v>122</v>
+        <v>58</v>
+      </c>
+      <c r="E8">
+        <v>206</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -3131,28 +3459,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
-      </c>
-      <c r="E9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>315</v>
-      </c>
-      <c r="H9" t="s">
-        <v>122</v>
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>180.5</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -3160,65 +3479,56 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>314</v>
-      </c>
-      <c r="H10" t="s">
-        <v>122</v>
+        <v>62</v>
+      </c>
+      <c r="E10">
+        <v>26.8</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>171</v>
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1284.2</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -3226,7 +3536,7 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -3234,15 +3544,15 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3250,7 +3560,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -3258,15 +3568,15 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>23.3</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -3274,7 +3584,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -3282,7 +3592,7 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>20</v>
@@ -3290,42 +3600,42 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3336,10 +3646,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3356,322 +3666,205 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3">
+        <v>181.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4">
+        <v>206.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5">
+        <v>160.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6">
+        <v>183.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7">
+        <v>192.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>307</v>
-      </c>
-      <c r="H2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="B9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9">
+        <v>219.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10">
+        <v>156.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1334.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>311</v>
-      </c>
-      <c r="H3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" t="s">
-        <v>178</v>
-      </c>
-      <c r="E4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>319</v>
-      </c>
-      <c r="H4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>355</v>
-      </c>
-      <c r="H5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" t="s">
-        <v>184</v>
-      </c>
-      <c r="E6" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>345</v>
-      </c>
-      <c r="H6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D7" t="s">
-        <v>187</v>
-      </c>
-      <c r="E7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>367</v>
-      </c>
-      <c r="H7" t="s">
-        <v>122</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>407</v>
-      </c>
-      <c r="H8" t="s">
-        <v>122</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D9" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" t="s">
-        <v>194</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>347</v>
-      </c>
-      <c r="H9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>195</v>
-      </c>
-      <c r="D10" t="s">
-        <v>193</v>
-      </c>
-      <c r="E10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>328</v>
-      </c>
-      <c r="H10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -3679,15 +3872,15 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3695,7 +3888,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -3703,15 +3896,15 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>34.71</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -3719,7 +3912,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -3727,50 +3920,50 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3781,10 +3974,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3801,330 +3994,213 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1140</v>
-      </c>
-      <c r="H2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1281</v>
-      </c>
-      <c r="H3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="E3">
+        <v>161.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>1369</v>
-      </c>
-      <c r="H4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="E4">
+        <v>117.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>207</v>
-      </c>
-      <c r="E5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>1322</v>
-      </c>
-      <c r="H5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="E5">
+        <v>193.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>210</v>
-      </c>
-      <c r="E6" t="s">
-        <v>211</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>1717</v>
-      </c>
-      <c r="H6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="E6">
+        <v>237.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>213</v>
-      </c>
-      <c r="E7" t="s">
-        <v>214</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1610</v>
-      </c>
-      <c r="H7" t="s">
-        <v>122</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="E7">
+        <v>193.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>216</v>
-      </c>
-      <c r="E8" t="s">
-        <v>217</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>1347</v>
-      </c>
-      <c r="H8" t="s">
-        <v>122</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="E8">
+        <v>164.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>219</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1000</v>
-      </c>
-      <c r="H9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+      <c r="E9">
+        <v>152.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>220</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" t="s">
-        <v>221</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>994</v>
-      </c>
-      <c r="H10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+      <c r="E10">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1262.5999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -4132,7 +4208,7 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4140,7 +4216,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -4148,15 +4224,15 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>52.58</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4164,7 +4240,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4172,23 +4248,23 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E24">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -4196,23 +4272,23 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4226,6 +4302,391 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H1" t="s">
+        <v>216</v>
+      </c>
+      <c r="I1" t="s">
+        <v>217</v>
+      </c>
+      <c r="J1" t="s">
+        <v>218</v>
+      </c>
+      <c r="K1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2">
+        <v>6.4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3">
+        <v>187.6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4">
+        <v>192.6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>219</v>
+      </c>
+      <c r="H4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I4" t="s">
+        <v>220</v>
+      </c>
+      <c r="J4" t="s">
+        <v>221</v>
+      </c>
+      <c r="K4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5">
+        <v>193</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6">
+        <v>126.4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7">
+        <v>162.80000000000001</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8">
+        <v>224.3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10">
+        <v>56.4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1166.0999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -4246,290 +4707,200 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" t="s">
-        <v>223</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1071</v>
-      </c>
-      <c r="H2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
+        <v>114</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1143</v>
-      </c>
-      <c r="H3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
+        <v>114</v>
+      </c>
+      <c r="E3">
+        <v>172.7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>229</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>1230</v>
-      </c>
-      <c r="H4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
+        <v>117</v>
+      </c>
+      <c r="E4">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>1108</v>
-      </c>
-      <c r="H5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
+        <v>119</v>
+      </c>
+      <c r="E5">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="F5" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>236</v>
-      </c>
-      <c r="E6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>1279</v>
-      </c>
-      <c r="H6" t="s">
-        <v>122</v>
+        <v>121</v>
+      </c>
+      <c r="E6">
+        <v>222</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c r="C7" t="s">
-        <v>238</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" t="s">
-        <v>240</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1141</v>
-      </c>
-      <c r="H7" t="s">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="E7">
+        <v>166.7</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s">
-        <v>242</v>
-      </c>
-      <c r="E8" t="s">
-        <v>243</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>1249</v>
-      </c>
-      <c r="H8" t="s">
-        <v>122</v>
+        <v>125</v>
+      </c>
+      <c r="E8">
+        <v>160.80000000000001</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="D9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E9" t="s">
-        <v>246</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1036</v>
-      </c>
-      <c r="H9" t="s">
-        <v>122</v>
+        <v>127</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>248</v>
-      </c>
-      <c r="E10" t="s">
-        <v>249</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>1742</v>
-      </c>
-      <c r="H10" t="s">
-        <v>122</v>
+        <v>127</v>
+      </c>
+      <c r="E10">
+        <v>28.6</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>250</v>
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>1166.3</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -4537,7 +4908,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -4545,7 +4916,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -4553,15 +4924,15 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4569,15 +4940,15 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4585,7 +4956,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -4593,15 +4964,15 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E21">
-        <v>28.78</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4609,7 +4980,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4617,15 +4988,15 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -4633,7 +5004,7 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -4641,23 +5012,23 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E29">
         <v>0</v>
